--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133894888</v>
       </c>
       <c r="B5" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91949</v>
+        <v>91968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133894884</v>
       </c>
       <c r="B3" t="n">
-        <v>44177</v>
+        <v>44182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133894878</v>
       </c>
       <c r="B4" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133894888</v>
       </c>
       <c r="B5" t="n">
-        <v>91949</v>
+        <v>91968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>133894883</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133894888</v>
       </c>
       <c r="B5" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133894888</v>
       </c>
       <c r="B5" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133894888</v>
       </c>
       <c r="B5" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133894877</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133894884</v>
+        <v>133894888</v>
       </c>
       <c r="B3" t="n">
-        <v>44182</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573726</v>
+        <v>573747</v>
       </c>
       <c r="R3" t="n">
-        <v>6531458</v>
+        <v>6531475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133894878</v>
+        <v>133894884</v>
       </c>
       <c r="B4" t="n">
-        <v>8449</v>
+        <v>44182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573725</v>
+        <v>573726</v>
       </c>
       <c r="R4" t="n">
-        <v>6531463</v>
+        <v>6531458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133894888</v>
+        <v>133894883</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>8460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573747</v>
+        <v>573764</v>
       </c>
       <c r="R5" t="n">
-        <v>6531475</v>
+        <v>6531434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133894883</v>
+        <v>133894878</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573764</v>
+        <v>573725</v>
       </c>
       <c r="R6" t="n">
-        <v>6531434</v>
+        <v>6531463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,6 +1157,200 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121648615</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalvshäll, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573338</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6531476</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133894882</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalvshäll, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573677</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6531627</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47886-2023 artfynd.xlsx
+++ b/artfynd/A 47886-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894878</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648615</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133894882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>